--- a/data/trans_orig/CAGE_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/CAGE_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE) en 2007</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5643</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>469105</t>
+          <t>469070</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>301037</t>
+          <t>301748</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>774567</t>
+          <t>774576</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7389</t>
+          <t>7813</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>963</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9133</t>
+          <t>8160</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>359545</t>
+          <t>359121</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>366990</t>
+          <t>366743</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>729666</t>
+          <t>730639</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>737829</t>
+          <t>737836</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>10220</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10127</t>
+          <t>10262</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>531839</t>
+          <t>532169</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>540665</t>
+          <t>540687</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>165831</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>167782</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>700044</t>
+          <t>699909</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>708488</t>
+          <t>708400</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21131</t>
+          <t>22125</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9187</t>
+          <t>8266</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>8811</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26138</t>
+          <t>25315</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1217203</t>
+          <t>1216209</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1231638</t>
+          <t>1231134</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>705098</t>
+          <t>706019</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1926482</t>
+          <t>1927305</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1943754</t>
+          <t>1943809</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>972</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11441</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15396</t>
+          <t>15010</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>341232</t>
+          <t>341555</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>349634</t>
+          <t>349583</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>557311</t>
+          <t>558754</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>567738</t>
+          <t>567734</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>903911</t>
+          <t>904297</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>916294</t>
+          <t>916052</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>292901</t>
+          <t>292787</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1243258</t>
+          <t>1243643</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1540655</t>
+          <t>1540671</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16580</t>
+          <t>17416</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37591</t>
+          <t>38326</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17949</t>
+          <t>17683</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,42 +2846,42 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>34927</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>24613</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>48851</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>0,53%</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>34927</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>25151</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>49074</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3232599</t>
+          <t>3231864</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3253610</t>
+          <t>3252774</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3360175</t>
+          <t>3360441</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3374150</t>
+          <t>3374207</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,47 +2954,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>99,88%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>6470</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>6613387</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>6599463</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6623701</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
           <t>99,47%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,88%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>6470</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>6613387</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>6599240</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>6623163</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>99,47%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE) en 2012</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>3790</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>16261</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16735</t>
+          <t>16915</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>421643</t>
+          <t>420950</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>433501</t>
+          <t>433421</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>312329</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>314454</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>734930</t>
+          <t>734750</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>747974</t>
+          <t>748518</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>990</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17436</t>
+          <t>15859</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5713</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17878</t>
+          <t>17564</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401361</t>
+          <t>402938</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417812</t>
+          <t>417807</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>332298</t>
+          <t>331634</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>738930</t>
+          <t>739244</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>754689</t>
+          <t>754645</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21855</t>
+          <t>23159</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22419</t>
+          <t>22743</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>607560</t>
+          <t>606256</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>623626</t>
+          <t>623219</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>258091</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>260129</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>867125</t>
+          <t>866801</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>883806</t>
+          <t>883687</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15373</t>
+          <t>14943</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35703</t>
+          <t>34253</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14787</t>
+          <t>15585</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34787</t>
+          <t>36043</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1123306</t>
+          <t>1124756</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1143636</t>
+          <t>1144066</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>761679</t>
+          <t>760644</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1890880</t>
+          <t>1889624</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1910880</t>
+          <t>1910082</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16849</t>
+          <t>16764</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19531</t>
+          <t>19606</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>493747</t>
+          <t>493832</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>505833</t>
+          <t>505973</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>755444</t>
+          <t>754366</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1252587</t>
+          <t>1252512</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1266347</t>
+          <t>1265747</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14549</t>
+          <t>13224</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15303</t>
+          <t>15209</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252333</t>
+          <t>253658</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263877</t>
+          <t>263935</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1104409</t>
+          <t>1104397</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1360930</t>
+          <t>1361024</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1372925</t>
+          <t>1372360</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>50049</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85396</t>
+          <t>86151</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11408</t>
+          <t>11105</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53641</t>
+          <t>54487</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90875</t>
+          <t>91002</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3336514</t>
+          <t>3335759</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3371997</t>
+          <t>3371861</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3538717</t>
+          <t>3539020</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3548131</t>
+          <t>3548134</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6881160</t>
+          <t>6881033</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6918394</t>
+          <t>6917548</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE) en 2016</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13390</t>
+          <t>13288</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>12043</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3739</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17800</t>
+          <t>18378</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>415702</t>
+          <t>415804</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428007</t>
+          <t>428028</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>335754</t>
+          <t>335012</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>758347</t>
+          <t>757769</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>772408</t>
+          <t>772415</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>916</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,47 +6361,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3181</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9098</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3181</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9019</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12770</t>
+          <t>13578</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>367811</t>
+          <t>368581</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376292</t>
+          <t>376311</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,49 +6474,49 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>99,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>369092</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>363175</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>371331</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
           <t>99,75%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>369092</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>363254</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>371333</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,58%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,75%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>700</t>
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>736730</t>
+          <t>735922</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>747313</t>
+          <t>746877</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4144</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16296</t>
+          <t>16999</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7091</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18900</t>
+          <t>19921</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>505618</t>
+          <t>504915</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517770</t>
+          <t>517915</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158806</t>
+          <t>159032</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>669136</t>
+          <t>668115</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>682699</t>
+          <t>682463</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10118</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27645</t>
+          <t>27887</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>826</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8004</t>
+          <t>8303</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>12298</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30848</t>
+          <t>32211</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1121993</t>
+          <t>1121751</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1139520</t>
+          <t>1139911</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>817872</t>
+          <t>817573</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>825053</t>
+          <t>825050</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1944666</t>
+          <t>1943303</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1963838</t>
+          <t>1963216</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16544</t>
+          <t>16808</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>6382</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7430,37 +7430,37 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>10063</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>4988</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>18559</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>0,74%</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>10063</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>4917</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>18623</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>604162</t>
+          <t>603898</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>616593</t>
+          <t>616854</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>732746</t>
+          <t>731862</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7538,39 +7538,39 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>99,14%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1287</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1348887</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1340391</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1353962</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>99,26%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1287</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1348887</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1340327</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1354033</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
           <t>98,63%</t>
@@ -7578,7 +7578,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12635</t>
+          <t>13169</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>951</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9752</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16615</t>
+          <t>16829</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>274510</t>
+          <t>273976</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>285105</t>
+          <t>284357</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1072322</t>
+          <t>1072273</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1081079</t>
+          <t>1081074</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1352555</t>
+          <t>1352341</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1364406</t>
+          <t>1364434</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36763</t>
+          <t>35386</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65792</t>
+          <t>64007</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>9738</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28290</t>
+          <t>26091</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51664</t>
+          <t>50640</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85504</t>
+          <t>84500</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3319930</t>
+          <t>3321715</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3348959</t>
+          <t>3350336</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3503306</t>
+          <t>3505505</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3521561</t>
+          <t>3521858</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6831814</t>
+          <t>6832818</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6865654</t>
+          <t>6866678</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE) en 2023</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13448</t>
+          <t>12375</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>509</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5887</t>
+          <t>6142</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>3962</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14399</t>
+          <t>14870</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>266755</t>
+          <t>267828</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>277150</t>
+          <t>277485</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>152223</t>
+          <t>151968</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>157607</t>
+          <t>157601</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>423914</t>
+          <t>423443</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>434083</t>
+          <t>434351</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5691</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>839</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6368</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>9425</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>205971</t>
+          <t>205659</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>211493</t>
+          <t>211495</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>125312</t>
+          <t>125147</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>130800</t>
+          <t>130841</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>333848</t>
+          <t>333917</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>341303</t>
+          <t>341300</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12759</t>
+          <t>11373</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2425</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12507</t>
+          <t>13442</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>198536</t>
+          <t>199922</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>208951</t>
+          <t>209410</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39214</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>239121</t>
+          <t>238186</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>249203</t>
+          <t>249126</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>7438</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25451</t>
+          <t>25327</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27368</t>
+          <t>28374</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>482849</t>
+          <t>482973</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>501263</t>
+          <t>500862</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>405619</t>
+          <t>405699</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>892789</t>
+          <t>891783</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>914150</t>
+          <t>914070</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13400</t>
+          <t>14406</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>981</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6424</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5515</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17033</t>
+          <t>17475</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>217733</t>
+          <t>216727</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>227444</t>
+          <t>227620</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>124699</t>
+          <t>124890</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130093</t>
+          <t>130142</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>345224</t>
+          <t>344782</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>356742</t>
+          <t>356012</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -10353,97 +10353,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2228</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4530</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>11404</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>9,39%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>2228</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>11422</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>10555</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>2228</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>11196</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90330</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109980</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>205066</t>
+          <t>205707</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24874</t>
+          <t>24448</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49692</t>
+          <t>47807</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5372</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20140</t>
+          <t>20155</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33218</t>
+          <t>32081</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64544</t>
+          <t>63736</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1487761</t>
+          <t>1489646</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1512579</t>
+          <t>1513005</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>974365</t>
+          <t>974350</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>989235</t>
+          <t>989133</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2467414</t>
+          <t>2468222</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2498740</t>
+          <t>2499877</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/CAGE_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/CAGE_R-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5881</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>469070</t>
+          <t>469065</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>301748</t>
+          <t>302096</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>774576</t>
+          <t>773573</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7813</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>960</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>359121</t>
+          <t>359622</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>366743</t>
+          <t>366647</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>730639</t>
+          <t>730515</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>737836</t>
+          <t>737839</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10220</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10262</t>
+          <t>9992</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>532169</t>
+          <t>532246</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>540687</t>
+          <t>540677</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>699909</t>
+          <t>700179</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>708400</t>
+          <t>708548</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22125</t>
+          <t>22053</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>8970</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8811</t>
+          <t>9222</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25315</t>
+          <t>26260</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1216209</t>
+          <t>1216281</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1231134</t>
+          <t>1231150</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>706019</t>
+          <t>705315</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1927305</t>
+          <t>1926360</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1943809</t>
+          <t>1943398</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>911</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>9524</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>10490</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15010</t>
+          <t>15485</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>341555</t>
+          <t>341031</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>349583</t>
+          <t>349644</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>558754</t>
+          <t>558262</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>567734</t>
+          <t>567725</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>904297</t>
+          <t>903822</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>916052</t>
+          <t>915663</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>292787</t>
+          <t>291761</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1243643</t>
+          <t>1243375</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1540671</t>
+          <t>1539613</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17416</t>
+          <t>16198</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38326</t>
+          <t>37731</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,82 +2806,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>9289</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>4152</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>18144</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>34927</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>25307</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>49437</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>0,53%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>9289</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>3917</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>17683</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>34927</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>24613</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>48851</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3231864</t>
+          <t>3232459</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3252774</t>
+          <t>3253992</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,82 +2919,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>99,5%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>3288</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>3368835</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>3359980</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3373972</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>99,88%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>6470</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>6613387</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>6598877</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6623007</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
           <t>99,47%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>3288</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>3368835</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>3360441</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>3374207</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,88%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>6470</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>6613387</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>6599463</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>6623701</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>99,47%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3790</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16261</t>
+          <t>16080</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16915</t>
+          <t>17209</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>420950</t>
+          <t>421131</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>433421</t>
+          <t>433498</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>734750</t>
+          <t>734456</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>748518</t>
+          <t>747952</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>983</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15859</t>
+          <t>17363</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17564</t>
+          <t>18690</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>402938</t>
+          <t>401434</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417807</t>
+          <t>417814</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>331634</t>
+          <t>332243</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>739244</t>
+          <t>738118</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>754645</t>
+          <t>754686</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23159</t>
+          <t>22589</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22743</t>
+          <t>24407</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>606256</t>
+          <t>606826</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>623219</t>
+          <t>623620</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>866801</t>
+          <t>865137</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>883687</t>
+          <t>883583</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14943</t>
+          <t>15008</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34253</t>
+          <t>34599</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15585</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36043</t>
+          <t>36253</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1124756</t>
+          <t>1124410</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1144066</t>
+          <t>1144001</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>760644</t>
+          <t>760970</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1889624</t>
+          <t>1889414</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1910082</t>
+          <t>1909874</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4623</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16764</t>
+          <t>16343</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7156</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>5885</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19606</t>
+          <t>19466</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>493832</t>
+          <t>494253</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>505973</t>
+          <t>505970</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>754366</t>
+          <t>754470</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1252512</t>
+          <t>1252652</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1265747</t>
+          <t>1266233</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13224</t>
+          <t>14205</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3873</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15209</t>
+          <t>15238</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253658</t>
+          <t>252677</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263935</t>
+          <t>263917</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1104397</t>
+          <t>1103889</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1361024</t>
+          <t>1360995</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1372360</t>
+          <t>1372480</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50049</t>
+          <t>50083</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86151</t>
+          <t>84144</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11105</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54487</t>
+          <t>53311</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91002</t>
+          <t>90202</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3335759</t>
+          <t>3337766</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3371861</t>
+          <t>3371827</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3539020</t>
+          <t>3538851</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3548134</t>
+          <t>3548133</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6881033</t>
+          <t>6881833</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6917548</t>
+          <t>6918724</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13288</t>
+          <t>13725</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12043</t>
+          <t>11908</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18378</t>
+          <t>17420</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>415804</t>
+          <t>415367</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428028</t>
+          <t>428026</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>335012</t>
+          <t>335147</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>346131</t>
+          <t>346123</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>757769</t>
+          <t>758727</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>772415</t>
+          <t>772453</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>939</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9098</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13578</t>
+          <t>13133</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>368581</t>
+          <t>368586</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376311</t>
+          <t>377227</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>363175</t>
+          <t>363736</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>371331</t>
+          <t>371334</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>735922</t>
+          <t>736367</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>746877</t>
+          <t>747416</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16999</t>
+          <t>16816</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>6487</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19921</t>
+          <t>18762</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>504915</t>
+          <t>505098</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517915</t>
+          <t>517799</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159032</t>
+          <t>159636</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>668115</t>
+          <t>669274</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>682463</t>
+          <t>682901</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27887</t>
+          <t>27550</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>815</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8303</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7087,34 +7087,34 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>19938</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>12187</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>31686</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>19938</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>12298</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>32211</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,62%</t>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1121751</t>
+          <t>1122088</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1139911</t>
+          <t>1139839</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>817573</t>
+          <t>818186</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>825050</t>
+          <t>825061</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,42 +7195,42 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1883</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1955576</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1943828</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1963327</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>98,99%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1883</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1955576</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1943303</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1963216</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,99%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16808</t>
+          <t>17811</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18559</t>
+          <t>18970</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>603898</t>
+          <t>602895</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>616854</t>
+          <t>616588</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>731862</t>
+          <t>732117</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1340391</t>
+          <t>1339980</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1353962</t>
+          <t>1354019</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13169</t>
+          <t>12016</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9752</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16829</t>
+          <t>17652</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>273976</t>
+          <t>275129</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>284357</t>
+          <t>284394</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1072273</t>
+          <t>1072474</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1081074</t>
+          <t>1080961</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1352341</t>
+          <t>1351518</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1364434</t>
+          <t>1364326</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35386</t>
+          <t>35537</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64007</t>
+          <t>63606</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9738</t>
+          <t>10026</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26091</t>
+          <t>27187</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50640</t>
+          <t>50366</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84500</t>
+          <t>85033</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3321715</t>
+          <t>3322116</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3350336</t>
+          <t>3350185</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3505505</t>
+          <t>3504409</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3521858</t>
+          <t>3521570</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6832818</t>
+          <t>6832285</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6866678</t>
+          <t>6866952</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12375</t>
+          <t>15987</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>536</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8294</t>
+          <t>10448</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14870</t>
+          <t>17909</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>273852</t>
+          <t>292620</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>267828</t>
+          <t>285076</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>277485</t>
+          <t>297165</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>156167</t>
+          <t>168750</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>151968</t>
+          <t>165142</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>157601</t>
+          <t>170219</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>430019</t>
+          <t>461369</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>423443</t>
+          <t>453908</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>434351</t>
+          <t>466632</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>280203</t>
+          <t>301063</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>280203</t>
+          <t>301063</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>280203</t>
+          <t>301063</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>158110</t>
+          <t>170755</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>158110</t>
+          <t>170755</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>158110</t>
+          <t>170755</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>438313</t>
+          <t>471817</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>438313</t>
+          <t>471817</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>438313</t>
+          <t>471817</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>8152</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9425</t>
+          <t>11865</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>209911</t>
+          <t>220788</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>205659</t>
+          <t>216073</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>211495</t>
+          <t>222679</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>128898</t>
+          <t>139265</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>125147</t>
+          <t>134742</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>130841</t>
+          <t>141487</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>338809</t>
+          <t>360053</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>333917</t>
+          <t>354391</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>341300</t>
+          <t>363195</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>211662</t>
+          <t>223362</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>211662</t>
+          <t>223362</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>211662</t>
+          <t>223362</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>131680</t>
+          <t>142894</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>131680</t>
+          <t>142894</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>131680</t>
+          <t>142894</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>343342</t>
+          <t>366256</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>343342</t>
+          <t>366256</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>343342</t>
+          <t>366256</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11373</t>
+          <t>17156</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13442</t>
+          <t>15907</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>205352</t>
+          <t>220163</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>199922</t>
+          <t>210953</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>209410</t>
+          <t>224849</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>245685</t>
+          <t>266728</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>238186</t>
+          <t>258767</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>249126</t>
+          <t>271555</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>211295</t>
+          <t>228109</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>211295</t>
+          <t>228109</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>211295</t>
+          <t>228109</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>251628</t>
+          <t>274674</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>251628</t>
+          <t>274674</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>251628</t>
+          <t>274674</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13791</t>
+          <t>12615</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7438</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25327</t>
+          <t>21815</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>15817</t>
+          <t>16783</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28374</t>
+          <t>28604</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>494509</t>
+          <t>527656</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>482973</t>
+          <t>518456</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>500862</t>
+          <t>533450</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>409831</t>
+          <t>223338</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>405699</t>
+          <t>214385</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>411857</t>
+          <t>226472</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>904340</t>
+          <t>750993</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>891783</t>
+          <t>739172</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>914070</t>
+          <t>757601</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>508300</t>
+          <t>540271</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>508300</t>
+          <t>540271</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>508300</t>
+          <t>540271</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>411857</t>
+          <t>227505</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>411857</t>
+          <t>227505</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>411857</t>
+          <t>227505</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>920157</t>
+          <t>767776</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>920157</t>
+          <t>767776</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>920157</t>
+          <t>767776</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>8758</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14406</t>
+          <t>15939</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>6490</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>11688</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6245</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17475</t>
+          <t>19261</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>223824</t>
+          <t>248236</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>216727</t>
+          <t>241055</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>227620</t>
+          <t>252727</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>128352</t>
+          <t>150318</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>124890</t>
+          <t>146758</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130142</t>
+          <t>152061</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>352178</t>
+          <t>398554</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>344782</t>
+          <t>390981</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>356012</t>
+          <t>403505</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>231133</t>
+          <t>256994</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>231133</t>
+          <t>256994</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>231133</t>
+          <t>256994</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>131123</t>
+          <t>153248</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>131123</t>
+          <t>153248</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>131123</t>
+          <t>153248</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>362257</t>
+          <t>410242</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>362257</t>
+          <t>410242</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>362257</t>
+          <t>410242</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11404</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -10428,12 +10428,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -10461,7 +10461,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -10496,27 +10496,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>119174</t>
+          <t>124247</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>114842</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>126471</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10531,27 +10531,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>214034</t>
+          <t>210088</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>205707</t>
+          <t>201033</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>212312</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>126471</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>126471</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>126471</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>212312</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>212312</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>212312</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,69 +10691,69 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>35145</t>
+          <t>40337</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24448</t>
+          <t>28319</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47807</t>
+          <t>55684</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>14955</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>8841</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>26976</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
           <t>3,11%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>11749</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>5372</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>20155</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>60</t>
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>46894</t>
+          <t>55293</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32081</t>
+          <t>41851</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63736</t>
+          <t>72607</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -10804,67 +10804,67 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1502308</t>
+          <t>1595303</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1489646</t>
+          <t>1579956</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1513005</t>
+          <t>1607321</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>96,6%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>98,27%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>852482</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>840461</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>858596</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>98,28%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
           <t>96,89%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>98,41%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1150</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>982756</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>974350</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>989133</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>97,97%</t>
-        </is>
-      </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2485064</t>
+          <t>2447783</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2468222</t>
+          <t>2430469</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2499877</t>
+          <t>2461225</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1537453</t>
+          <t>1635640</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1537453</t>
+          <t>1635640</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1537453</t>
+          <t>1635640</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>994505</t>
+          <t>867437</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>994505</t>
+          <t>867437</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>994505</t>
+          <t>867437</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2531958</t>
+          <t>2503076</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2531958</t>
+          <t>2503076</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2531958</t>
+          <t>2503076</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
